--- a/InputData/elec/BDSBaPCF/Boolean Do Suppliers Bid at Peak Capacity Factors.xlsx
+++ b/InputData/elec/BDSBaPCF/Boolean Do Suppliers Bid at Peak Capacity Factors.xlsx
@@ -1,27 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25225"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\World Resources Institute\TRAC City - HK 2050 is now\EPS HK 2.0\eps-hongkong-develop\InputData\elec\BDSBaPCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\BDSBaPCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{B7EC880F-D7B8-4EFF-B441-7D939866CE6C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{0D8CBD1A-1ADA-41C9-9853-44EEB2867D60}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A1020E-B0C4-4F04-8009-3AA729898980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BDSBaPCF" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -29,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>BDSBaPCF Boolean Do Suppliers Bid at Peak Capacity Factors</t>
   </si>
@@ -139,14 +143,20 @@
     <t>Do Suppliers Bid at Peak Capacity Factors (Boolean)</t>
   </si>
   <si>
-    <t>set value for coal to 0, because HK  has commend control to reduce coal</t>
+    <t>For the United States, we have set coal to 0 as of version 3.4. This reflects</t>
+  </si>
+  <si>
+    <t>the fact that certain air quality / environmental restrictions, as well as current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supply chain logistics, limit the amount the coal dispatches annually. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,13 +168,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -190,13 +193,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,15 +537,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -551,89 +553,99 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -647,18 +659,18 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.54296875" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -666,7 +678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -674,15 +686,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -690,7 +702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -698,7 +710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -706,7 +718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -714,7 +726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -722,7 +734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -730,7 +742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -738,7 +750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -746,7 +758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -755,7 +767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -764,7 +776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -773,7 +785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -782,12 +794,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>34</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <f>B9</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -796,40 +809,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -837,24 +842,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -873,70 +939,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -1038,7 +1057,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1048,47 +1067,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1305797A-D163-424F-9B8B-59B3462947D9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFFD1F81-DBCF-475F-916E-6396CA4CE9A8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81E1AC9E-FC70-4462-837A-1C977CE36C45}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A079EC84-DA3C-4D91-B4C2-A208014F60BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD58F13C-D7C9-435D-8768-24E9AE1B893A}"/>
 </file>